--- a/MICS/Methods/bh.xlsx
+++ b/MICS/Methods/bh.xlsx
@@ -1,21 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23001"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28914"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fau-my.sharepoint.com/personal/dbastola2022_fau_edu/Documents/Academics/Research/Malnutrition/MICS/Methods/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_085D8E7FD670C60F623554765804A6FE8A57AD65" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{3AB48664-EF54-46D6-AA66-95390EF52764}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_085D8E7FD670C60F623554765804A6FE8A57AD65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AB48664-EF54-46D6-AA66-95390EF52764}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -347,7 +363,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -708,14 +724,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C54"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="52.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -726,7 +742,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -737,7 +753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -748,7 +764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -759,7 +775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -770,7 +786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -781,7 +797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
@@ -792,7 +808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
@@ -803,7 +819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -814,7 +830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
@@ -825,7 +841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
         <v>19</v>
       </c>
@@ -836,7 +852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
         <v>21</v>
       </c>
@@ -847,7 +863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
         <v>23</v>
       </c>
@@ -858,7 +874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
         <v>25</v>
       </c>
@@ -869,7 +885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
         <v>27</v>
       </c>
@@ -880,7 +896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
         <v>29</v>
       </c>
@@ -891,7 +907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
         <v>31</v>
       </c>
@@ -902,7 +918,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
         <v>33</v>
       </c>
@@ -913,7 +929,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
         <v>35</v>
       </c>
@@ -924,7 +940,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
         <v>37</v>
       </c>
@@ -935,7 +951,7 @@
         <v>26015</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
         <v>39</v>
       </c>
@@ -946,7 +962,7 @@
         <v>26015</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
         <v>41</v>
       </c>
@@ -957,7 +973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
         <v>43</v>
       </c>
@@ -968,7 +984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
         <v>45</v>
       </c>
@@ -979,7 +995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" s="2" t="s">
         <v>47</v>
       </c>
@@ -990,7 +1006,7 @@
         <v>26015</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" s="2" t="s">
         <v>49</v>
       </c>
@@ -1001,7 +1017,7 @@
         <v>26015</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" s="2" t="s">
         <v>51</v>
       </c>
@@ -1012,7 +1028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" s="2" t="s">
         <v>53</v>
       </c>
@@ -1023,7 +1039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29" s="2" t="s">
         <v>55</v>
       </c>
@@ -1034,7 +1050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30" s="2" t="s">
         <v>57</v>
       </c>
@@ -1045,7 +1061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3">
       <c r="A31" s="2" t="s">
         <v>59</v>
       </c>
@@ -1056,7 +1072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3">
       <c r="A32" s="2" t="s">
         <v>61</v>
       </c>
@@ -1067,7 +1083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
         <v>63</v>
       </c>
@@ -1078,7 +1094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
         <v>65</v>
       </c>
@@ -1089,7 +1105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3">
       <c r="A35" s="2" t="s">
         <v>67</v>
       </c>
@@ -1100,7 +1116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3">
       <c r="A36" s="2" t="s">
         <v>69</v>
       </c>
@@ -1111,7 +1127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3">
       <c r="A37" s="2" t="s">
         <v>71</v>
       </c>
@@ -1122,7 +1138,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3">
       <c r="A38" s="2" t="s">
         <v>73</v>
       </c>
@@ -1133,7 +1149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3">
       <c r="A39" s="2" t="s">
         <v>75</v>
       </c>
@@ -1144,7 +1160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3">
       <c r="A40" s="2" t="s">
         <v>77</v>
       </c>
@@ -1155,7 +1171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3">
       <c r="A41" s="2" t="s">
         <v>79</v>
       </c>
@@ -1166,7 +1182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3">
       <c r="A42" s="2" t="s">
         <v>81</v>
       </c>
@@ -1177,7 +1193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3">
       <c r="A43" s="2" t="s">
         <v>83</v>
       </c>
@@ -1188,7 +1204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3">
       <c r="A44" s="2" t="s">
         <v>85</v>
       </c>
@@ -1199,7 +1215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3">
       <c r="A45" s="2" t="s">
         <v>87</v>
       </c>
@@ -1210,7 +1226,7 @@
         <v>12339</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3">
       <c r="A46" s="2" t="s">
         <v>89</v>
       </c>
@@ -1221,7 +1237,7 @@
         <v>12339</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3">
       <c r="A47" s="2" t="s">
         <v>91</v>
       </c>
@@ -1232,7 +1248,7 @@
         <v>12339</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3">
       <c r="A48" s="2" t="s">
         <v>93</v>
       </c>
@@ -1243,7 +1259,7 @@
         <v>15006</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3">
       <c r="A49" s="2" t="s">
         <v>95</v>
       </c>
@@ -1254,7 +1270,7 @@
         <v>15006</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3">
       <c r="A50" s="2" t="s">
         <v>97</v>
       </c>
@@ -1265,7 +1281,7 @@
         <v>15006</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3">
       <c r="A51" s="2" t="s">
         <v>99</v>
       </c>
@@ -1276,7 +1292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3">
       <c r="A52" s="2" t="s">
         <v>101</v>
       </c>
@@ -1287,7 +1303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3">
       <c r="A53" s="2" t="s">
         <v>103</v>
       </c>
@@ -1298,7 +1314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3">
       <c r="A54" s="2" t="s">
         <v>105</v>
       </c>
